--- a/data/trans_orig/P70A_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P70A_2023-Clase-trans_orig.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W32"/>
+  <dimension ref="A1:W28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si dichos problemas de salud fueron causados por su trabajo en 2023</t>
+          <t>Población según si su ausencia en el trabajo por motivos de salud, fue debido a problemas de salud causados por su trabajo en 2023 (tasa de respuesta: 94,01%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>72819</t>
+          <t>72645</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>87319</t>
+          <t>87510</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>76,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>77490</t>
+          <t>77114</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>90288</t>
+          <t>90290</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>154786</t>
+          <t>154432</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>174737</t>
+          <t>174527</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>78,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>88,56%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>1788</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11830</t>
+          <t>11779</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4627</t>
+          <t>4377</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14465</t>
+          <t>14085</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7976</t>
+          <t>8024</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>21216</t>
+          <t>21693</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>11,01%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4139</t>
+          <t>3738</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16311</t>
+          <t>15635</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5223</t>
+          <t>4837</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14157</t>
+          <t>14061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>11043</t>
+          <t>11525</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>26074</t>
+          <t>28011</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>14,21%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>46850</t>
+          <t>47146</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>61409</t>
+          <t>62063</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>65,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>55161</t>
+          <t>53245</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>68350</t>
+          <t>67468</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,29%</t>
+          <t>70,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>105418</t>
+          <t>107419</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>127126</t>
+          <t>127473</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,57%</t>
+          <t>72,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>86,54%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7097</t>
+          <t>6987</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20547</t>
+          <t>20619</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1717</t>
+          <t>1815</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9040</t>
+          <t>8968</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>9995</t>
+          <t>10310</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>24968</t>
+          <t>25390</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,24%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1178</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10084</t>
+          <t>10507</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4011</t>
+          <t>4026</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16651</t>
+          <t>17798</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6879</t>
+          <t>6341</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23340</t>
+          <t>21796</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>14,8%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>224476</t>
+          <t>226756</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>298764</t>
+          <t>298054</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>74,96%</t>
+          <t>75,72%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8114</t>
+          <t>8417</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13425</t>
+          <t>13364</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>54,65%</t>
+          <t>56,69%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>236277</t>
+          <t>236262</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>311631</t>
+          <t>311797</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,2%</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35465</t>
+          <t>35886</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>388</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3779</t>
+          <t>4092</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>292</t>
+          <t>736</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37800</t>
+          <t>36104</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,49%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>440</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>44363</t>
+          <t>42539</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>481</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5245</t>
+          <t>4515</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>1190</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>45491</t>
+          <t>46392</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,76%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>57450</t>
+          <t>58074</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>80556</t>
+          <t>80882</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>52,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>72,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>76584</t>
+          <t>76972</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>93743</t>
+          <t>93790</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>66,48%</t>
+          <t>66,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>81,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>143056</t>
+          <t>141131</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>171840</t>
+          <t>168767</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>63,1%</t>
+          <t>62,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>74,44%</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8517</t>
+          <t>8570</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24409</t>
+          <t>25211</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8144</t>
+          <t>8228</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19656</t>
+          <t>19200</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>18919</t>
+          <t>19056</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>39274</t>
+          <t>39956</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,62%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17582</t>
+          <t>17672</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>38487</t>
+          <t>38056</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>10109</t>
+          <t>9893</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>24814</t>
+          <t>24052</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>30262</t>
+          <t>32091</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>55234</t>
+          <t>56619</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,97%</t>
         </is>
       </c>
     </row>
@@ -2554,12 +2554,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>35298</t>
+          <t>34690</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>49694</t>
+          <t>49827</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>61,24%</t>
+          <t>60,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>32959</t>
+          <t>33109</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>45889</t>
+          <t>45778</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>51,86%</t>
+          <t>52,09%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>72,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>71445</t>
+          <t>72620</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>91134</t>
+          <t>91620</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>59,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>75,6%</t>
         </is>
       </c>
     </row>
@@ -2667,12 +2667,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3099</t>
+          <t>3025</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>15209</t>
+          <t>15777</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7146</t>
+          <t>7354</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>17428</t>
+          <t>17473</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>13090</t>
+          <t>12649</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>29278</t>
+          <t>28225</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2752,12 +2752,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>23,29%</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2722</t>
+          <t>2767</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14247</t>
+          <t>14902</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7425</t>
+          <t>7372</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18027</t>
+          <t>18350</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2830,12 +2830,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>13178</t>
+          <t>12858</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>28583</t>
+          <t>27192</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>22,44%</t>
         </is>
       </c>
     </row>
@@ -2990,7 +2990,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -3000,107 +3000,107 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>273</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>536859</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>467033</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>600689</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>84,43%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>73,45%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>407</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>284668</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>267820</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>297270</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>76,79%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>72,24%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>680</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>821527</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>754949</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>908519</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>81,62%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>75,0%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>90,26%</t>
         </is>
       </c>
     </row>
@@ -3113,107 +3113,107 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>44</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>45996</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>12333</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>79937</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>63</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>39038</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>30072</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>49484</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>107</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>85034</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>43438</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>118491</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,77%</t>
         </is>
       </c>
     </row>
@@ -3226,107 +3226,107 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>50</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>53004</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>19251</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>95172</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>64</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>47019</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>37299</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>60919</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>114</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>100023</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>49039</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>139188</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,83%</t>
         </is>
       </c>
     </row>
@@ -3339,580 +3339,123 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>367</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>635859</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>635859</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>635859</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>534</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>370724</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>370724</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>370724</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>901</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1006583</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1006583</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1006583</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>536859</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>463817</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>598000</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>84,43%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>72,94%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>94,05%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>407</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>284668</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>268465</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>297615</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>76,79%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>72,42%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>80,28%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>680</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>821527</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>752644</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>911251</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>81,62%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>74,77%</t>
-        </is>
-      </c>
-      <c r="W28" s="2" t="inlineStr">
-        <is>
-          <t>90,53%</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="n"/>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>Sí, parcialmente</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>45996</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>14621</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>83661</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>7,23%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>2,3%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>13,16%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>39038</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>30084</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>49992</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>10,53%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>8,11%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>13,49%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>85034</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>39127</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>120437</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>8,45%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>3,89%</t>
-        </is>
-      </c>
-      <c r="W29" s="2" t="inlineStr">
-        <is>
-          <t>11,96%</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="n"/>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>Sí, totalmente</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>53004</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>18363</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>93124</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>8,34%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>2,89%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>14,65%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>47019</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>36468</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>61182</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>12,68%</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>9,84%</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>16,5%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>100023</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>47344</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>140528</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>9,94%</t>
-        </is>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>4,7%</t>
-        </is>
-      </c>
-      <c r="W30" s="2" t="inlineStr">
-        <is>
-          <t>13,96%</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="n"/>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>367</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>635859</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>635859</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>635859</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>534</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>370724</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>370724</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>370724</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>901</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>1006583</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t>1006583</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="inlineStr">
-        <is>
-          <t>1006583</t>
-        </is>
-      </c>
-      <c r="U31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A4:A7"/>
     <mergeCell ref="A8:A11"/>
     <mergeCell ref="A12:A15"/>
-    <mergeCell ref="A28:A31"/>
     <mergeCell ref="A20:A23"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="Q1:W1"/>

--- a/data/trans_orig/P70A_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P70A_2023-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>80928</t>
+          <t>86725</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>72645</t>
+          <t>77845</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>87510</t>
+          <t>92638</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>85,7%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>76,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>84709</t>
+          <t>88113</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>77114</t>
+          <t>80355</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>90290</t>
+          <t>93419</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>82,99%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>75,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>165638</t>
+          <t>174838</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>154432</t>
+          <t>163308</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>174527</t>
+          <t>183443</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>88,46%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5433</t>
+          <t>5493</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1788</t>
+          <t>2039</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11779</t>
+          <t>12118</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8335</t>
+          <t>8974</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4377</t>
+          <t>4810</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14085</t>
+          <t>15458</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>13768</t>
+          <t>14467</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8024</t>
+          <t>8774</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>21693</t>
+          <t>22708</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,95%</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8862</t>
+          <t>8980</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3738</t>
+          <t>3973</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15635</t>
+          <t>16469</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>8808</t>
+          <t>9083</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4837</t>
+          <t>5443</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14061</t>
+          <t>14992</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>17670</t>
+          <t>18062</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>11525</t>
+          <t>11423</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>28011</t>
+          <t>26527</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>12,79%</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>95223</t>
+          <t>101198</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>95223</t>
+          <t>101198</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>95223</t>
+          <t>101198</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>101852</t>
+          <t>106170</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>101852</t>
+          <t>106170</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>101852</t>
+          <t>106170</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>197076</t>
+          <t>207368</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>197076</t>
+          <t>207368</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>197076</t>
+          <t>207368</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>55150</t>
+          <t>56126</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>47146</t>
+          <t>48103</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>62063</t>
+          <t>62782</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>76,57%</t>
+          <t>76,35%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,45%</t>
+          <t>65,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>85,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>62792</t>
+          <t>65733</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>53245</t>
+          <t>57951</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>67468</t>
+          <t>71030</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>83,64%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,75%</t>
+          <t>73,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>117943</t>
+          <t>121859</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>107419</t>
+          <t>111158</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>127473</t>
+          <t>130345</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>80,12%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,93%</t>
+          <t>73,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>85,7%</t>
         </is>
       </c>
     </row>
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12663</t>
+          <t>12187</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6987</t>
+          <t>6801</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20619</t>
+          <t>19511</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4368</t>
+          <t>4398</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1815</t>
+          <t>1428</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8968</t>
+          <t>8922</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>17031</t>
+          <t>16585</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>10310</t>
+          <t>10459</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>25390</t>
+          <t>25250</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>16,6%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>4217</t>
+          <t>5198</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1716</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10507</t>
+          <t>11785</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,17 +1442,17 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>8101</t>
+          <t>8460</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4026</t>
+          <t>4288</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17798</t>
+          <t>17045</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>12318</t>
+          <t>13657</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6341</t>
+          <t>7955</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21796</t>
+          <t>23903</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>15,72%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>72030</t>
+          <t>73511</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>72030</t>
+          <t>73511</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>72030</t>
+          <t>73511</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>75261</t>
+          <t>78590</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>75261</t>
+          <t>78590</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>75261</t>
+          <t>78590</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>147291</t>
+          <t>152101</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>147291</t>
+          <t>152101</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>147291</t>
+          <t>152101</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,32 +1637,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>287709</t>
+          <t>49678</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>226756</t>
+          <t>42133</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>298054</t>
+          <t>55042</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>80,97%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>68,67%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,32 +1672,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11398</t>
+          <t>11995</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8417</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13364</t>
+          <t>14309</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>76,76%</t>
+          <t>74,06%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>56,69%</t>
+          <t>50,32%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>88,34%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>299105</t>
+          <t>61672</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>236262</t>
+          <t>53216</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>311797</t>
+          <t>67978</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>79,53%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>75,17%</t>
+          <t>68,62%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>87,66%</t>
         </is>
       </c>
     </row>
@@ -1750,32 +1750,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5232</t>
+          <t>5239</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2103</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35886</t>
+          <t>12443</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1785,32 +1785,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1543</t>
+          <t>2150</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>553</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4092</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>6775</t>
+          <t>7389</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>736</t>
+          <t>3601</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>36104</t>
+          <t>14177</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>18,28%</t>
         </is>
       </c>
     </row>
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>6521</t>
+          <t>6436</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>2870</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>42539</t>
+          <t>12415</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1909</t>
+          <t>2053</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>481</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4515</t>
+          <t>5531</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>8430</t>
+          <t>8489</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1190</t>
+          <t>4390</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>46392</t>
+          <t>15213</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>19,62%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>299462</t>
+          <t>61354</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>299462</t>
+          <t>61354</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>299462</t>
+          <t>61354</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14849</t>
+          <t>16197</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>14849</t>
+          <t>16197</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>14849</t>
+          <t>16197</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>314310</t>
+          <t>77550</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>314310</t>
+          <t>77550</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>314310</t>
+          <t>77550</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,32 +2093,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>70079</t>
+          <t>75830</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>58074</t>
+          <t>63419</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>80882</t>
+          <t>87527</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>62,85%</t>
+          <t>63,2%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>52,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>72,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,32 +2128,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>86263</t>
+          <t>98754</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>76972</t>
+          <t>88304</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>93790</t>
+          <t>106258</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>76,52%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>66,81%</t>
+          <t>68,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>156342</t>
+          <t>174584</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>141131</t>
+          <t>159471</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>168767</t>
+          <t>188131</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>68,96%</t>
+          <t>70,1%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>62,25%</t>
+          <t>64,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>75,54%</t>
         </is>
       </c>
     </row>
@@ -2206,32 +2206,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>14979</t>
+          <t>16990</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8570</t>
+          <t>9845</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25211</t>
+          <t>26442</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,32 +2241,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>12941</t>
+          <t>13619</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8228</t>
+          <t>8218</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19200</t>
+          <t>20593</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>27920</t>
+          <t>30608</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>19056</t>
+          <t>22180</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>39956</t>
+          <t>41709</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>16,75%</t>
         </is>
       </c>
     </row>
@@ -2319,32 +2319,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>26446</t>
+          <t>27173</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17672</t>
+          <t>17817</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>38056</t>
+          <t>39661</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>16003</t>
+          <t>16676</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>9893</t>
+          <t>11078</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>24052</t>
+          <t>26816</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>42450</t>
+          <t>43849</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>32091</t>
+          <t>31474</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>56619</t>
+          <t>57437</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>23,06%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>111504</t>
+          <t>119994</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>111504</t>
+          <t>119994</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>111504</t>
+          <t>119994</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>115207</t>
+          <t>129048</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>115207</t>
+          <t>129048</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>115207</t>
+          <t>129048</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>226711</t>
+          <t>249041</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>226711</t>
+          <t>249041</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>226711</t>
+          <t>249041</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2549,32 +2549,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>42993</t>
+          <t>50519</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>34690</t>
+          <t>41103</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>49827</t>
+          <t>57923</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>75,28%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>60,18%</t>
+          <t>61,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,32 +2584,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>39505</t>
+          <t>48084</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>33109</t>
+          <t>41020</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>45778</t>
+          <t>54867</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>62,16%</t>
+          <t>64,54%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>55,06%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,03%</t>
+          <t>73,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>82499</t>
+          <t>98603</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>72620</t>
+          <t>87114</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>91620</t>
+          <t>108951</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>68,07%</t>
+          <t>69,63%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>59,92%</t>
+          <t>61,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,6%</t>
+          <t>76,94%</t>
         </is>
       </c>
     </row>
@@ -2662,32 +2662,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7689</t>
+          <t>8253</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3025</t>
+          <t>3413</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>15777</t>
+          <t>16107</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,32 +2697,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>11852</t>
+          <t>13472</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7354</t>
+          <t>8409</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>17473</t>
+          <t>19476</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,32 +2732,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>19540</t>
+          <t>21725</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>12649</t>
+          <t>14511</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>28225</t>
+          <t>31426</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>22,19%</t>
         </is>
       </c>
     </row>
@@ -2775,32 +2775,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>6958</t>
+          <t>8336</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2767</t>
+          <t>3865</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14902</t>
+          <t>16944</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,32 +2810,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>12198</t>
+          <t>12949</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7372</t>
+          <t>7903</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18350</t>
+          <t>19298</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,32 +2845,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>19156</t>
+          <t>21285</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>12858</t>
+          <t>13535</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>27192</t>
+          <t>31231</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,05%</t>
         </is>
       </c>
     </row>
@@ -2888,17 +2888,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>57640</t>
+          <t>67108</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>57640</t>
+          <t>67108</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>57640</t>
+          <t>67108</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2923,17 +2923,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>63555</t>
+          <t>74505</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>63555</t>
+          <t>74505</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>63555</t>
+          <t>74505</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>121195</t>
+          <t>141613</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>121195</t>
+          <t>141613</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>121195</t>
+          <t>141613</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3005,102 +3005,102 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>536859</t>
+          <t>318878</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>467033</t>
+          <t>297658</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>600689</t>
+          <t>338159</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>75,36%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
+          <t>70,34%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>79,91%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>407</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>312678</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>296194</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>326923</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>77,3%</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>73,22%</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>80,82%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>631557</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>607901</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>656476</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>76,3%</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
           <t>73,45%</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>94,47%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>407</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>284668</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>267820</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>297270</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>76,79%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>72,24%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>80,19%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>680</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>821527</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>754949</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>908519</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>81,62%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>75,0%</t>
-        </is>
-      </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>79,32%</t>
         </is>
       </c>
     </row>
@@ -3118,32 +3118,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>45996</t>
+          <t>48163</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12333</t>
+          <t>35381</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>79937</t>
+          <t>63249</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,17 +3153,17 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>39038</t>
+          <t>42612</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>30072</t>
+          <t>33280</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>49484</t>
+          <t>53550</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3173,47 +3173,47 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
+          <t>13,24%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>90775</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>76217</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>110527</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>10,97%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>9,21%</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
           <t>13,35%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>85034</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>43438</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>118491</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>8,45%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>4,32%</t>
-        </is>
-      </c>
-      <c r="W25" s="2" t="inlineStr">
-        <is>
-          <t>11,77%</t>
         </is>
       </c>
     </row>
@@ -3231,32 +3231,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>53004</t>
+          <t>56123</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>19251</t>
+          <t>42587</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>95172</t>
+          <t>74278</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,32 +3266,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>47019</t>
+          <t>49219</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>37299</t>
+          <t>39291</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>60919</t>
+          <t>63550</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,32 +3301,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>100023</t>
+          <t>105343</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>49039</t>
+          <t>86294</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>139188</t>
+          <t>125703</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>15,19%</t>
         </is>
       </c>
     </row>
@@ -3344,17 +3344,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>635859</t>
+          <t>423165</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>635859</t>
+          <t>423165</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>635859</t>
+          <t>423165</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3379,17 +3379,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>370724</t>
+          <t>404509</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>370724</t>
+          <t>404509</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>370724</t>
+          <t>404509</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3414,17 +3414,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1006583</t>
+          <t>827674</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1006583</t>
+          <t>827674</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1006583</t>
+          <t>827674</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
